--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{988532F9-7CAA-496B-A965-EADB460C5D2C}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B55B5119-E9AF-430B-A5B3-006B5958EFCB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2008,11 +2008,11 @@
         <v>39</v>
       </c>
       <c r="I30" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J30" s="9">
         <f>I30-H30</f>
-        <v>-34</v>
+        <v>-23</v>
       </c>
       <c r="K30">
         <v>28</v>
@@ -2067,11 +2067,11 @@
         <v>27</v>
       </c>
       <c r="I31" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" ref="J31:J40" si="10">I31-H31</f>
-        <v>-22</v>
+        <v>-14</v>
       </c>
       <c r="K31">
         <v>20</v>
@@ -2126,11 +2126,11 @@
         <v>32</v>
       </c>
       <c r="I32" s="1">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J32" s="9">
         <f t="shared" si="10"/>
-        <v>-24</v>
+        <v>-9</v>
       </c>
       <c r="K32">
         <v>22</v>
@@ -2185,11 +2185,11 @@
         <v>51</v>
       </c>
       <c r="I33" s="1">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="10"/>
-        <v>-34</v>
+        <v>-19</v>
       </c>
       <c r="K33">
         <v>37</v>
@@ -2244,11 +2244,11 @@
         <v>32</v>
       </c>
       <c r="I34" s="1">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="10"/>
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K34">
         <v>22</v>
@@ -2303,11 +2303,11 @@
         <v>35</v>
       </c>
       <c r="I35" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="10"/>
-        <v>-27</v>
+        <v>-20</v>
       </c>
       <c r="K35">
         <v>24</v>
@@ -2362,11 +2362,11 @@
         <v>35</v>
       </c>
       <c r="I36" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="10"/>
-        <v>-31</v>
+        <v>-28</v>
       </c>
       <c r="K36">
         <v>25</v>
@@ -2421,11 +2421,11 @@
         <v>55</v>
       </c>
       <c r="I37" s="1">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="10"/>
-        <v>-42</v>
+        <v>-28</v>
       </c>
       <c r="K37">
         <v>40</v>
@@ -2480,11 +2480,11 @@
         <v>39</v>
       </c>
       <c r="I38" s="1">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J38" s="9">
         <f t="shared" si="10"/>
-        <v>-32</v>
+        <v>-23</v>
       </c>
       <c r="K38">
         <v>28</v>
@@ -2539,11 +2539,11 @@
         <v>40</v>
       </c>
       <c r="I39" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J39" s="9">
         <f t="shared" si="10"/>
-        <v>-35</v>
+        <v>-24</v>
       </c>
       <c r="K39">
         <v>28</v>
@@ -2598,11 +2598,11 @@
         <v>13</v>
       </c>
       <c r="I40" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="10"/>
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="K40">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>
-        <v>-316</v>
+        <v>-209</v>
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B55B5119-E9AF-430B-A5B3-006B5958EFCB}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB55A8C-0293-4215-852B-F79DE0E7155A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2008,11 +2008,11 @@
         <v>39</v>
       </c>
       <c r="I30" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J30" s="9">
         <f>I30-H30</f>
-        <v>-23</v>
+        <v>-15</v>
       </c>
       <c r="K30">
         <v>28</v>
@@ -2067,11 +2067,11 @@
         <v>27</v>
       </c>
       <c r="I31" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" ref="J31:J40" si="10">I31-H31</f>
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="K31">
         <v>20</v>
@@ -2126,11 +2126,11 @@
         <v>32</v>
       </c>
       <c r="I32" s="1">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J32" s="9">
         <f t="shared" si="10"/>
-        <v>-9</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>22</v>
@@ -2185,11 +2185,11 @@
         <v>51</v>
       </c>
       <c r="I33" s="1">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="10"/>
-        <v>-19</v>
+        <v>-6</v>
       </c>
       <c r="K33">
         <v>37</v>
@@ -2244,11 +2244,11 @@
         <v>32</v>
       </c>
       <c r="I34" s="1">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="10"/>
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="K34">
         <v>22</v>
@@ -2303,11 +2303,11 @@
         <v>35</v>
       </c>
       <c r="I35" s="1">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="10"/>
-        <v>-20</v>
+        <v>-7</v>
       </c>
       <c r="K35">
         <v>24</v>
@@ -2362,11 +2362,11 @@
         <v>35</v>
       </c>
       <c r="I36" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="10"/>
-        <v>-28</v>
+        <v>-22</v>
       </c>
       <c r="K36">
         <v>25</v>
@@ -2421,11 +2421,11 @@
         <v>55</v>
       </c>
       <c r="I37" s="1">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="10"/>
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="K37">
         <v>40</v>
@@ -2480,11 +2480,11 @@
         <v>39</v>
       </c>
       <c r="I38" s="1">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J38" s="9">
         <f t="shared" si="10"/>
-        <v>-23</v>
+        <v>-9</v>
       </c>
       <c r="K38">
         <v>28</v>
@@ -2539,11 +2539,11 @@
         <v>40</v>
       </c>
       <c r="I39" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J39" s="9">
         <f t="shared" si="10"/>
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="K39">
         <v>28</v>
@@ -2598,11 +2598,11 @@
         <v>13</v>
       </c>
       <c r="I40" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="10"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="K40">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>
-        <v>-209</v>
+        <v>-105</v>
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB55A8C-0293-4215-852B-F79DE0E7155A}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57463E45-6281-4EB2-A721-3D2B959F99C8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="11976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
@@ -295,7 +295,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -2008,11 +2008,11 @@
         <v>39</v>
       </c>
       <c r="I30" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J30" s="9">
         <f>I30-H30</f>
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="K30">
         <v>28</v>
@@ -2067,11 +2067,11 @@
         <v>27</v>
       </c>
       <c r="I31" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" ref="J31:J40" si="10">I31-H31</f>
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="K31">
         <v>20</v>
@@ -2126,11 +2126,11 @@
         <v>32</v>
       </c>
       <c r="I32" s="1">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J32" s="9">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K32">
         <v>22</v>
@@ -2185,11 +2185,11 @@
         <v>51</v>
       </c>
       <c r="I33" s="1">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="10"/>
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>37</v>
@@ -2244,11 +2244,11 @@
         <v>32</v>
       </c>
       <c r="I34" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="10"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>22</v>
@@ -2303,11 +2303,11 @@
         <v>35</v>
       </c>
       <c r="I35" s="1">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="10"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="K35">
         <v>24</v>
@@ -2362,11 +2362,11 @@
         <v>35</v>
       </c>
       <c r="I36" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="10"/>
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="K36">
         <v>25</v>
@@ -2421,11 +2421,11 @@
         <v>55</v>
       </c>
       <c r="I37" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="10"/>
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="K37">
         <v>40</v>
@@ -2480,11 +2480,11 @@
         <v>39</v>
       </c>
       <c r="I38" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J38" s="9">
         <f t="shared" si="10"/>
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="K38">
         <v>28</v>
@@ -2539,11 +2539,11 @@
         <v>40</v>
       </c>
       <c r="I39" s="1">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J39" s="9">
         <f t="shared" si="10"/>
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="K39">
         <v>28</v>
@@ -2598,11 +2598,11 @@
         <v>13</v>
       </c>
       <c r="I40" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>
-        <v>-105</v>
+        <v>-29</v>
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57463E45-6281-4EB2-A721-3D2B959F99C8}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB5AE18E-F3D7-416A-92CD-4DACA7FF779B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="11976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2008,19 +2008,21 @@
         <v>39</v>
       </c>
       <c r="I30" s="1">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J30" s="9">
         <f>I30-H30</f>
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="K30">
         <v>28</v>
       </c>
-      <c r="L30" s="1"/>
+      <c r="L30" s="1">
+        <v>2</v>
+      </c>
       <c r="M30" s="9">
         <f>L30-K30</f>
-        <v>-28</v>
+        <v>-26</v>
       </c>
       <c r="N30">
         <v>33</v>
@@ -2067,19 +2069,21 @@
         <v>27</v>
       </c>
       <c r="I31" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" ref="J31:J40" si="10">I31-H31</f>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="K31">
         <v>20</v>
       </c>
-      <c r="L31" s="1"/>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="9">
         <f t="shared" ref="M31:M40" si="11">L31-K31</f>
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="N31">
         <v>23</v>
@@ -2126,19 +2130,21 @@
         <v>32</v>
       </c>
       <c r="I32" s="1">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J32" s="9">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K32">
         <v>22</v>
       </c>
-      <c r="L32" s="1"/>
+      <c r="L32" s="1">
+        <v>2</v>
+      </c>
       <c r="M32" s="9">
         <f t="shared" si="11"/>
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="N32">
         <v>27</v>
@@ -2185,19 +2191,21 @@
         <v>51</v>
       </c>
       <c r="I33" s="1">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K33">
         <v>37</v>
       </c>
-      <c r="L33" s="1"/>
+      <c r="L33" s="1">
+        <v>4</v>
+      </c>
       <c r="M33" s="9">
         <f t="shared" si="11"/>
-        <v>-37</v>
+        <v>-33</v>
       </c>
       <c r="N33">
         <v>43</v>
@@ -2244,19 +2252,21 @@
         <v>32</v>
       </c>
       <c r="I34" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K34">
         <v>22</v>
       </c>
-      <c r="L34" s="1"/>
+      <c r="L34" s="1">
+        <v>1</v>
+      </c>
       <c r="M34" s="9">
         <f t="shared" si="11"/>
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="N34">
         <v>25</v>
@@ -2303,19 +2313,21 @@
         <v>35</v>
       </c>
       <c r="I35" s="1">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J35" s="9">
         <f t="shared" si="10"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>24</v>
       </c>
-      <c r="L35" s="1"/>
+      <c r="L35" s="1">
+        <v>2</v>
+      </c>
       <c r="M35" s="9">
         <f t="shared" si="11"/>
-        <v>-24</v>
+        <v>-22</v>
       </c>
       <c r="N35">
         <v>28</v>
@@ -2362,16 +2374,18 @@
         <v>35</v>
       </c>
       <c r="I36" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J36" s="9">
         <f t="shared" si="10"/>
-        <v>-21</v>
+        <v>-17</v>
       </c>
       <c r="K36">
         <v>25</v>
       </c>
-      <c r="L36" s="1"/>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
       <c r="M36" s="9">
         <f t="shared" si="11"/>
         <v>-25</v>
@@ -2421,19 +2435,21 @@
         <v>55</v>
       </c>
       <c r="I37" s="1">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J37" s="9">
         <f t="shared" si="10"/>
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="K37">
         <v>40</v>
       </c>
-      <c r="L37" s="1"/>
+      <c r="L37" s="1">
+        <v>2</v>
+      </c>
       <c r="M37" s="9">
         <f t="shared" si="11"/>
-        <v>-40</v>
+        <v>-38</v>
       </c>
       <c r="N37">
         <v>45</v>
@@ -2480,19 +2496,21 @@
         <v>39</v>
       </c>
       <c r="I38" s="1">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J38" s="9">
         <f t="shared" si="10"/>
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="K38">
         <v>28</v>
       </c>
-      <c r="L38" s="1"/>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
       <c r="M38" s="9">
         <f t="shared" si="11"/>
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="N38">
         <v>31</v>
@@ -2539,19 +2557,21 @@
         <v>40</v>
       </c>
       <c r="I39" s="1">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J39" s="9">
         <f t="shared" si="10"/>
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="K39">
         <v>28</v>
       </c>
-      <c r="L39" s="1"/>
+      <c r="L39" s="1">
+        <v>2</v>
+      </c>
       <c r="M39" s="9">
         <f t="shared" si="11"/>
-        <v>-28</v>
+        <v>-26</v>
       </c>
       <c r="N39">
         <v>33</v>
@@ -2598,16 +2618,18 @@
         <v>13</v>
       </c>
       <c r="I40" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40">
         <v>10</v>
       </c>
-      <c r="L40" s="1"/>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
       <c r="M40" s="10">
         <f t="shared" si="11"/>
         <v>-10</v>
@@ -2656,11 +2678,11 @@
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>
-        <v>-29</v>
+        <v>24</v>
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>
-        <v>-284</v>
+        <v>-267</v>
       </c>
       <c r="P42">
         <f>SUM(P30:P41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB5AE18E-F3D7-416A-92CD-4DACA7FF779B}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EBF8F07-34BF-4C65-B8D7-91E383294445}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="11976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
@@ -2018,11 +2018,11 @@
         <v>28</v>
       </c>
       <c r="L30" s="1">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M30" s="9">
         <f>L30-K30</f>
-        <v>-26</v>
+        <v>-11</v>
       </c>
       <c r="N30">
         <v>33</v>
@@ -2079,11 +2079,11 @@
         <v>20</v>
       </c>
       <c r="L31" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M31" s="9">
         <f t="shared" ref="M31:M40" si="11">L31-K31</f>
-        <v>-19</v>
+        <v>-9</v>
       </c>
       <c r="N31">
         <v>23</v>
@@ -2140,11 +2140,11 @@
         <v>22</v>
       </c>
       <c r="L32" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M32" s="9">
         <f t="shared" si="11"/>
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="N32">
         <v>27</v>
@@ -2201,11 +2201,11 @@
         <v>37</v>
       </c>
       <c r="L33" s="1">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="11"/>
-        <v>-33</v>
+        <v>-20</v>
       </c>
       <c r="N33">
         <v>43</v>
@@ -2262,11 +2262,11 @@
         <v>22</v>
       </c>
       <c r="L34" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="11"/>
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="N34">
         <v>25</v>
@@ -2323,11 +2323,11 @@
         <v>24</v>
       </c>
       <c r="L35" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="11"/>
-        <v>-22</v>
+        <v>-13</v>
       </c>
       <c r="N35">
         <v>28</v>
@@ -2384,11 +2384,11 @@
         <v>25</v>
       </c>
       <c r="L36" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="11"/>
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="N36">
         <v>28</v>
@@ -2445,11 +2445,11 @@
         <v>40</v>
       </c>
       <c r="L37" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="11"/>
-        <v>-38</v>
+        <v>-27</v>
       </c>
       <c r="N37">
         <v>45</v>
@@ -2506,11 +2506,11 @@
         <v>28</v>
       </c>
       <c r="L38" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M38" s="9">
         <f t="shared" si="11"/>
-        <v>-27</v>
+        <v>-17</v>
       </c>
       <c r="N38">
         <v>31</v>
@@ -2567,11 +2567,11 @@
         <v>28</v>
       </c>
       <c r="L39" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="11"/>
-        <v>-26</v>
+        <v>-15</v>
       </c>
       <c r="N39">
         <v>33</v>
@@ -2628,11 +2628,11 @@
         <v>10</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="10">
         <f t="shared" si="11"/>
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="N40">
         <v>11</v>
@@ -2676,13 +2676,17 @@
         <f>SUM(G30:G41)</f>
         <v>15</v>
       </c>
+      <c r="I42">
+        <f>SUM(I30:I41)</f>
+        <v>422</v>
+      </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>
         <v>24</v>
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>
-        <v>-267</v>
+        <v>-164</v>
       </c>
       <c r="P42">
         <f>SUM(P30:P41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EBF8F07-34BF-4C65-B8D7-91E383294445}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53CF96AA-F979-4FED-A7FE-4582E1C38872}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2018,11 +2018,11 @@
         <v>28</v>
       </c>
       <c r="L30" s="1">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M30" s="9">
         <f>L30-K30</f>
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="N30">
         <v>33</v>
@@ -2079,11 +2079,11 @@
         <v>20</v>
       </c>
       <c r="L31" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M31" s="9">
         <f t="shared" ref="M31:M40" si="11">L31-K31</f>
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="N31">
         <v>23</v>
@@ -2201,11 +2201,11 @@
         <v>37</v>
       </c>
       <c r="L33" s="1">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="11"/>
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="N33">
         <v>43</v>
@@ -2262,11 +2262,11 @@
         <v>22</v>
       </c>
       <c r="L34" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="11"/>
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="N34">
         <v>25</v>
@@ -2323,11 +2323,11 @@
         <v>24</v>
       </c>
       <c r="L35" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="11"/>
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="N35">
         <v>28</v>
@@ -2384,11 +2384,11 @@
         <v>25</v>
       </c>
       <c r="L36" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="11"/>
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="N36">
         <v>28</v>
@@ -2445,11 +2445,11 @@
         <v>40</v>
       </c>
       <c r="L37" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="11"/>
-        <v>-27</v>
+        <v>-24</v>
       </c>
       <c r="N37">
         <v>45</v>
@@ -2506,11 +2506,11 @@
         <v>28</v>
       </c>
       <c r="L38" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M38" s="9">
         <f t="shared" si="11"/>
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="N38">
         <v>31</v>
@@ -2567,11 +2567,11 @@
         <v>28</v>
       </c>
       <c r="L39" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="N39">
         <v>33</v>
@@ -2628,11 +2628,11 @@
         <v>10</v>
       </c>
       <c r="L40" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M40" s="10">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="N40">
         <v>11</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>
-        <v>-164</v>
+        <v>-114</v>
       </c>
       <c r="P42">
         <f>SUM(P30:P41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53CF96AA-F979-4FED-A7FE-4582E1C38872}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C201C736-6593-489E-99C4-85523200CD0F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="11976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
@@ -2018,11 +2018,11 @@
         <v>28</v>
       </c>
       <c r="L30" s="1">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="M30" s="9">
         <f>L30-K30</f>
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>33</v>
@@ -2079,11 +2079,11 @@
         <v>20</v>
       </c>
       <c r="L31" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M31" s="9">
         <f t="shared" ref="M31:M40" si="11">L31-K31</f>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="N31">
         <v>23</v>
@@ -2140,11 +2140,11 @@
         <v>22</v>
       </c>
       <c r="L32" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M32" s="9">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="N32">
         <v>27</v>
@@ -2201,11 +2201,11 @@
         <v>37</v>
       </c>
       <c r="L33" s="1">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="N33">
         <v>43</v>
@@ -2262,11 +2262,11 @@
         <v>22</v>
       </c>
       <c r="L34" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="N34">
         <v>25</v>
@@ -2323,11 +2323,11 @@
         <v>24</v>
       </c>
       <c r="L35" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="N35">
         <v>28</v>
@@ -2384,11 +2384,11 @@
         <v>25</v>
       </c>
       <c r="L36" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="11"/>
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="N36">
         <v>28</v>
@@ -2445,11 +2445,11 @@
         <v>40</v>
       </c>
       <c r="L37" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="11"/>
-        <v>-24</v>
+        <v>-22</v>
       </c>
       <c r="N37">
         <v>45</v>
@@ -2506,11 +2506,11 @@
         <v>28</v>
       </c>
       <c r="L38" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M38" s="9">
         <f t="shared" si="11"/>
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="N38">
         <v>31</v>
@@ -2567,11 +2567,11 @@
         <v>28</v>
       </c>
       <c r="L39" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="N39">
         <v>33</v>
@@ -2628,11 +2628,11 @@
         <v>10</v>
       </c>
       <c r="L40" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M40" s="10">
         <f t="shared" si="11"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="N40">
         <v>11</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>
-        <v>-114</v>
+        <v>-41</v>
       </c>
       <c r="P42">
         <f>SUM(P30:P41)</f>
